--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5500</v>
+        <v>7500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>54500</v>
+        <v>52500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1214,9 +1214,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45698</v>
+      </c>
+      <c r="C14" s="4">
+        <v>500</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1240,9 +1246,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45699</v>
+      </c>
+      <c r="C15" s="4">
+        <v>500</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1266,9 +1278,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45699</v>
+      </c>
+      <c r="C16" s="4">
+        <v>500</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1292,9 +1310,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45700</v>
+      </c>
+      <c r="C17" s="4">
+        <v>500</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7500</v>
+        <v>9500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>52500</v>
+        <v>50500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1342,9 +1342,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45703</v>
+      </c>
+      <c r="C18" s="4">
+        <v>500</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1368,9 +1374,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45705</v>
+      </c>
+      <c r="C19" s="4">
+        <v>500</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1394,9 +1406,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45707</v>
+      </c>
+      <c r="C20" s="4">
+        <v>500</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1420,9 +1438,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45708</v>
+      </c>
+      <c r="C21" s="4">
+        <v>500</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9500</v>
+        <v>13000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>50500</v>
+        <v>47000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1470,9 +1470,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45713</v>
+      </c>
+      <c r="C22" s="4">
+        <v>500</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1496,9 +1502,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45714</v>
+      </c>
+      <c r="C23" s="4">
+        <v>500</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1522,9 +1534,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45715</v>
+      </c>
+      <c r="C24" s="4">
+        <v>500</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1548,9 +1566,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45718</v>
+      </c>
+      <c r="C25" s="4">
+        <v>500</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1574,9 +1598,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45720</v>
+      </c>
+      <c r="C26" s="4">
+        <v>500</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1600,9 +1630,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45722</v>
+      </c>
+      <c r="C27" s="4">
+        <v>500</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1626,9 +1662,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45723</v>
+      </c>
+      <c r="C28" s="4">
+        <v>500</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>13000</v>
+        <v>20500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>47000</v>
+        <v>39500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45737</v>
+      </c>
+      <c r="G3" s="4">
+        <v>500</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -906,9 +912,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45738</v>
+      </c>
+      <c r="G4" s="4">
+        <v>500</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -938,9 +950,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45742</v>
+      </c>
+      <c r="G5" s="4">
+        <v>500</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -970,9 +988,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45745</v>
+      </c>
+      <c r="G6" s="4">
+        <v>500</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1002,9 +1026,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45748</v>
+      </c>
+      <c r="G7" s="4">
+        <v>500</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1034,9 +1064,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45749</v>
+      </c>
+      <c r="G8" s="4">
+        <v>500</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1066,9 +1102,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45753</v>
+      </c>
+      <c r="G9" s="4">
+        <v>500</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1098,9 +1140,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45754</v>
+      </c>
+      <c r="G10" s="4">
+        <v>500</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1130,9 +1178,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45756</v>
+      </c>
+      <c r="G11" s="4">
+        <v>500</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1162,9 +1216,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45757</v>
+      </c>
+      <c r="G12" s="4">
+        <v>500</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1194,9 +1254,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45758</v>
+      </c>
+      <c r="G13" s="4">
+        <v>500</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1694,9 +1760,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45725</v>
+      </c>
+      <c r="C29" s="4">
+        <v>500</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1720,9 +1792,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45728</v>
+      </c>
+      <c r="C30" s="4">
+        <v>500</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1746,9 +1824,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45729</v>
+      </c>
+      <c r="C31" s="4">
+        <v>500</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1772,9 +1856,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45736</v>
+      </c>
+      <c r="C32" s="4">
+        <v>500</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>20500</v>
+        <v>27500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>39500</v>
+        <v>32500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1292,9 +1292,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45759</v>
+      </c>
+      <c r="G14" s="4">
+        <v>500</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1324,9 +1330,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45760</v>
+      </c>
+      <c r="G15" s="4">
+        <v>500</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1356,9 +1368,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45763</v>
+      </c>
+      <c r="G16" s="4">
+        <v>500</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1388,9 +1406,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45764</v>
+      </c>
+      <c r="G17" s="4">
+        <v>500</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1420,9 +1444,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45765</v>
+      </c>
+      <c r="G18" s="4">
+        <v>500</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1452,9 +1482,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45766</v>
+      </c>
+      <c r="G19" s="4">
+        <v>500</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1484,9 +1520,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45768</v>
+      </c>
+      <c r="G20" s="4">
+        <v>500</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1516,9 +1558,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45768</v>
+      </c>
+      <c r="G21" s="4">
+        <v>500</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1548,9 +1596,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45769</v>
+      </c>
+      <c r="G22" s="4">
+        <v>500</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1580,9 +1634,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45770</v>
+      </c>
+      <c r="G23" s="4">
+        <v>500</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1612,9 +1672,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45771</v>
+      </c>
+      <c r="G24" s="4">
+        <v>500</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1644,9 +1710,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45773</v>
+      </c>
+      <c r="G25" s="4">
+        <v>500</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1676,9 +1748,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45776</v>
+      </c>
+      <c r="G26" s="4">
+        <v>500</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1708,9 +1786,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45777</v>
+      </c>
+      <c r="G27" s="4">
+        <v>500</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>27500</v>
+        <v>32000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>32500</v>
+        <v>28000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45788</v>
+      </c>
+      <c r="K3" s="4">
+        <v>500</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -924,9 +930,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45789</v>
+      </c>
+      <c r="K4" s="4">
+        <v>500</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -962,9 +974,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45791</v>
+      </c>
+      <c r="K5" s="4">
+        <v>500</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -1000,9 +1018,15 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45792</v>
+      </c>
+      <c r="K6" s="4">
+        <v>500</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>
@@ -1824,9 +1848,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45779</v>
+      </c>
+      <c r="G28" s="4">
+        <v>500</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1856,9 +1886,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45781</v>
+      </c>
+      <c r="G29" s="4">
+        <v>500</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1888,9 +1924,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45784</v>
+      </c>
+      <c r="G30" s="4">
+        <v>500</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1920,9 +1962,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45785</v>
+      </c>
+      <c r="G31" s="4">
+        <v>500</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1952,9 +2000,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45786</v>
+      </c>
+      <c r="G32" s="4">
+        <v>500</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>32000</v>
+        <v>34000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1062,9 +1062,15 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45793</v>
+      </c>
+      <c r="K7" s="4">
+        <v>500</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
@@ -1100,9 +1106,15 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45794</v>
+      </c>
+      <c r="K8" s="4">
+        <v>500</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
@@ -1138,9 +1150,15 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45797</v>
+      </c>
+      <c r="K9" s="4">
+        <v>500</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
@@ -1176,9 +1194,15 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45799</v>
+      </c>
+      <c r="K10" s="4">
+        <v>500</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD20000.18-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>34000</v>
+        <v>34500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>26000</v>
+        <v>25500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1238,9 +1238,15 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45832</v>
+      </c>
+      <c r="K11" s="4">
+        <v>500</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -393,7 +393,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -428,7 +428,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>34500</v>
+        <v>35500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>25500</v>
+        <v>24500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1282,9 +1282,15 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45850</v>
+      </c>
+      <c r="K12" s="4">
+        <v>500</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
@@ -1320,9 +1326,15 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>45851</v>
+      </c>
+      <c r="K13" s="4">
+        <v>500</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>35500</v>
+        <v>36000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>24500</v>
+        <v>24000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1370,9 +1370,15 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>45856</v>
+      </c>
+      <c r="K14" s="4">
+        <v>500</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>36000</v>
+        <v>38000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1414,9 +1414,15 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>45866</v>
+      </c>
+      <c r="K15" s="4">
+        <v>500</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
@@ -1452,9 +1458,15 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>45869</v>
+      </c>
+      <c r="K16" s="4">
+        <v>500</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
@@ -1490,9 +1502,15 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>45870</v>
+      </c>
+      <c r="K17" s="4">
+        <v>500</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
@@ -1528,9 +1546,15 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>45874</v>
+      </c>
+      <c r="K18" s="4">
+        <v>500</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>38000</v>
+        <v>41000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1590,9 +1590,15 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>45884</v>
+      </c>
+      <c r="K19" s="4">
+        <v>500</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
@@ -1628,9 +1634,15 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>45886</v>
+      </c>
+      <c r="K20" s="4">
+        <v>500</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
@@ -1666,9 +1678,15 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>45888</v>
+      </c>
+      <c r="K21" s="4">
+        <v>500</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>
@@ -1704,9 +1722,15 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>45889</v>
+      </c>
+      <c r="K22" s="4">
+        <v>500</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
@@ -1742,9 +1766,15 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>45894</v>
+      </c>
+      <c r="K23" s="4">
+        <v>500</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
@@ -1780,9 +1810,15 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>45897</v>
+      </c>
+      <c r="K24" s="4">
+        <v>500</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>41000</v>
+        <v>45000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>19000</v>
+        <v>15000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1854,9 +1854,15 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>45899</v>
+      </c>
+      <c r="K25" s="4">
+        <v>500</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
@@ -1892,9 +1898,15 @@
       <c r="I26" s="1">
         <v>84</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
+      <c r="J26" s="3">
+        <v>45905</v>
+      </c>
+      <c r="K26" s="4">
+        <v>500</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
       <c r="M26" s="1">
         <v>114</v>
       </c>
@@ -1930,9 +1942,15 @@
       <c r="I27" s="1">
         <v>85</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="J27" s="3">
+        <v>45905</v>
+      </c>
+      <c r="K27" s="4">
+        <v>500</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
       <c r="M27" s="1">
         <v>115</v>
       </c>
@@ -1968,9 +1986,15 @@
       <c r="I28" s="1">
         <v>86</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="J28" s="3">
+        <v>45907</v>
+      </c>
+      <c r="K28" s="4">
+        <v>500</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
       <c r="M28" s="1">
         <v>116</v>
       </c>
@@ -2006,9 +2030,15 @@
       <c r="I29" s="1">
         <v>87</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
+      <c r="J29" s="3">
+        <v>45908</v>
+      </c>
+      <c r="K29" s="4">
+        <v>500</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
       <c r="M29" s="1">
         <v>117</v>
       </c>
@@ -2044,9 +2074,15 @@
       <c r="I30" s="1">
         <v>88</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="3">
+        <v>45913</v>
+      </c>
+      <c r="K30" s="4">
+        <v>500</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
       <c r="M30" s="1">
         <v>118</v>
       </c>
@@ -2082,9 +2118,15 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>45925</v>
+      </c>
+      <c r="K31" s="4">
+        <v>500</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
@@ -2120,9 +2162,15 @@
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>45927</v>
+      </c>
+      <c r="K32" s="4">
+        <v>500</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>45000</v>
+        <v>48500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>15000</v>
+        <v>11500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -898,9 +898,15 @@
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>45931</v>
+      </c>
+      <c r="O3" s="4">
+        <v>500</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -942,9 +948,15 @@
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>45933</v>
+      </c>
+      <c r="O4" s="4">
+        <v>500</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -986,9 +998,15 @@
       <c r="M5" s="1">
         <v>93</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="1"/>
+      <c r="N5" s="3">
+        <v>45934</v>
+      </c>
+      <c r="O5" s="4">
+        <v>500</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1030,9 +1048,15 @@
       <c r="M6" s="1">
         <v>94</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="1"/>
+      <c r="N6" s="3">
+        <v>45935</v>
+      </c>
+      <c r="O6" s="4">
+        <v>500</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1074,9 +1098,15 @@
       <c r="M7" s="1">
         <v>95</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="1"/>
+      <c r="N7" s="3">
+        <v>45936</v>
+      </c>
+      <c r="O7" s="4">
+        <v>500</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1118,9 +1148,15 @@
       <c r="M8" s="1">
         <v>96</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="1"/>
+      <c r="N8" s="3">
+        <v>45938</v>
+      </c>
+      <c r="O8" s="4">
+        <v>500</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1162,9 +1198,15 @@
       <c r="M9" s="1">
         <v>97</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="1"/>
+      <c r="N9" s="3">
+        <v>45941</v>
+      </c>
+      <c r="O9" s="4">
+        <v>500</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>48500</v>
+        <v>51500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11500</v>
+        <v>8500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1248,9 +1248,15 @@
       <c r="M10" s="1">
         <v>98</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="1"/>
+      <c r="N10" s="3">
+        <v>45942</v>
+      </c>
+      <c r="O10" s="4">
+        <v>500</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1292,9 +1298,15 @@
       <c r="M11" s="1">
         <v>99</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="1"/>
+      <c r="N11" s="3">
+        <v>45946</v>
+      </c>
+      <c r="O11" s="4">
+        <v>500</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1336,9 +1348,15 @@
       <c r="M12" s="1">
         <v>100</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="1"/>
+      <c r="N12" s="3">
+        <v>45947</v>
+      </c>
+      <c r="O12" s="4">
+        <v>500</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1380,9 +1398,15 @@
       <c r="M13" s="1">
         <v>101</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="1"/>
+      <c r="N13" s="3">
+        <v>45948</v>
+      </c>
+      <c r="O13" s="4">
+        <v>500</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1424,9 +1448,15 @@
       <c r="M14" s="1">
         <v>102</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="1"/>
+      <c r="N14" s="3">
+        <v>45949</v>
+      </c>
+      <c r="O14" s="4">
+        <v>500</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1468,9 +1498,15 @@
       <c r="M15" s="1">
         <v>103</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="1"/>
+      <c r="N15" s="3">
+        <v>45950</v>
+      </c>
+      <c r="O15" s="4">
+        <v>500</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>51500</v>
+        <v>55000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>8500</v>
+        <v>5000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1548,9 +1548,15 @@
       <c r="M16" s="1">
         <v>104</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="1"/>
+      <c r="N16" s="3">
+        <v>45959</v>
+      </c>
+      <c r="O16" s="4">
+        <v>500</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1592,9 +1598,15 @@
       <c r="M17" s="1">
         <v>105</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="1"/>
+      <c r="N17" s="3">
+        <v>45967</v>
+      </c>
+      <c r="O17" s="4">
+        <v>500</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -1636,9 +1648,15 @@
       <c r="M18" s="1">
         <v>106</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="1"/>
+      <c r="N18" s="3">
+        <v>45967</v>
+      </c>
+      <c r="O18" s="4">
+        <v>500</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1680,9 +1698,15 @@
       <c r="M19" s="1">
         <v>107</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="1"/>
+      <c r="N19" s="3">
+        <v>45967</v>
+      </c>
+      <c r="O19" s="4">
+        <v>500</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -1724,9 +1748,15 @@
       <c r="M20" s="1">
         <v>108</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="1"/>
+      <c r="N20" s="3">
+        <v>45967</v>
+      </c>
+      <c r="O20" s="4">
+        <v>500</v>
+      </c>
+      <c r="P20" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1768,9 +1798,15 @@
       <c r="M21" s="1">
         <v>109</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="1"/>
+      <c r="N21" s="3">
+        <v>45972</v>
+      </c>
+      <c r="O21" s="4">
+        <v>500</v>
+      </c>
+      <c r="P21" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1812,9 +1848,15 @@
       <c r="M22" s="1">
         <v>110</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="1"/>
+      <c r="N22" s="3">
+        <v>45972</v>
+      </c>
+      <c r="O22" s="4">
+        <v>500</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>55000</v>
+        <v>58000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1898,9 +1898,15 @@
       <c r="M23" s="1">
         <v>111</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="1"/>
+      <c r="N23" s="3">
+        <v>45978</v>
+      </c>
+      <c r="O23" s="4">
+        <v>500</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1942,9 +1948,15 @@
       <c r="M24" s="1">
         <v>112</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="1"/>
+      <c r="N24" s="3">
+        <v>45979</v>
+      </c>
+      <c r="O24" s="4">
+        <v>500</v>
+      </c>
+      <c r="P24" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -1986,9 +1998,15 @@
       <c r="M25" s="1">
         <v>113</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="1"/>
+      <c r="N25" s="3">
+        <v>45983</v>
+      </c>
+      <c r="O25" s="4">
+        <v>500</v>
+      </c>
+      <c r="P25" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -2030,9 +2048,15 @@
       <c r="M26" s="1">
         <v>114</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="1"/>
+      <c r="N26" s="3">
+        <v>45985</v>
+      </c>
+      <c r="O26" s="4">
+        <v>500</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -2074,9 +2098,15 @@
       <c r="M27" s="1">
         <v>115</v>
       </c>
-      <c r="N27" s="3"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="1"/>
+      <c r="N27" s="3">
+        <v>45987</v>
+      </c>
+      <c r="O27" s="4">
+        <v>500</v>
+      </c>
+      <c r="P27" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -2118,9 +2148,15 @@
       <c r="M28" s="1">
         <v>116</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="1"/>
+      <c r="N28" s="3">
+        <v>45988</v>
+      </c>
+      <c r="O28" s="4">
+        <v>500</v>
+      </c>
+      <c r="P28" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>58000</v>
+        <v>59500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -2198,9 +2198,15 @@
       <c r="M29" s="1">
         <v>117</v>
       </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="1"/>
+      <c r="N29" s="3">
+        <v>45992</v>
+      </c>
+      <c r="O29" s="4">
+        <v>500</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -2242,9 +2248,15 @@
       <c r="M30" s="1">
         <v>118</v>
       </c>
-      <c r="N30" s="3"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="1"/>
+      <c r="N30" s="3">
+        <v>45992</v>
+      </c>
+      <c r="O30" s="4">
+        <v>500</v>
+      </c>
+      <c r="P30" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -2286,9 +2298,15 @@
       <c r="M31" s="1">
         <v>119</v>
       </c>
-      <c r="N31" s="3"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="1"/>
+      <c r="N31" s="3">
+        <v>45993</v>
+      </c>
+      <c r="O31" s="4">
+        <v>500</v>
+      </c>
+      <c r="P31" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">

--- a/LoanOfficer-A/2023/93 joychandra.xlsx
+++ b/LoanOfficer-A/2023/93 joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>59500</v>
+        <v>60000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -2348,9 +2348,15 @@
       <c r="M32" s="1">
         <v>120</v>
       </c>
-      <c r="N32" s="3"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="1"/>
+      <c r="N32" s="3">
+        <v>46004</v>
+      </c>
+      <c r="O32" s="4">
+        <v>500</v>
+      </c>
+      <c r="P32" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
